--- a/acolyte_cards.xlsx
+++ b/acolyte_cards.xlsx
@@ -675,6 +675,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="29.28125"/>
+    <col customWidth="1" min="3" max="3" width="108.421875"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15">
       <c r="A1" s="1" t="s">
@@ -687,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="105">
+    <row r="2" ht="15">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -698,7 +702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="90">
+    <row r="3" ht="15">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -709,7 +713,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="75">
+    <row r="4" ht="28.5">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -720,7 +724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="120">
+    <row r="5" ht="30">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -731,7 +735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="75">
+    <row r="6" ht="15">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -742,7 +746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="165">
+    <row r="7" ht="30">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -753,7 +757,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="120">
+    <row r="8" ht="28.5">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -764,7 +768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="90">
+    <row r="9" ht="30">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -775,7 +779,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="75">
+    <row r="10" ht="30">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -786,7 +790,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="105">
+    <row r="11" ht="30">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>

--- a/acolyte_cards.xlsx
+++ b/acolyte_cards.xlsx
@@ -121,29 +121,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.000000"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,17 +149,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,123 +655,123 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="15">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="28.5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="30">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="15">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="30">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" ht="28.5">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" ht="30">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="30">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" ht="30">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>32</v>
       </c>
     </row>

--- a/acolyte_cards.xlsx
+++ b/acolyte_cards.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Holy Light</t>
   </si>
   <si>
-    <t xml:space="preserve">Heal 1. If healing another player: gain 1 resource.</t>
+    <t xml:space="preserve">Heal 2. If healing another player: gain 1 resource.</t>
   </si>
   <si>
     <t>cardimages/restore.png</t>
@@ -51,7 +51,7 @@
     <t>Consecration</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 to everyone; repeat next turn.</t>
+    <t xml:space="preserve">Deal 2 to everyone; repeat next turn.</t>
   </si>
   <si>
     <t>cardimages/seal_of_wisdom.png</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Righteous Defense</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 3. Take all damage players would take. Gather 1 per damage taken.</t>
+    <t xml:space="preserve">Prevent 6. Take all damage players would take. Gather 1 per damage taken.</t>
   </si>
   <si>
     <t>cardimages/judgement.png</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Execution Sentence</t>
   </si>
   <si>
-    <t xml:space="preserve">In 3 turns, deal 5 damage to monster.</t>
+    <t xml:space="preserve">In 3 turns, deal 10 damage to monster.</t>
   </si>
   <si>
     <t>cardimages/sacred_shield.png</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Sacred Shield</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 2 this turn and 2 next turn.</t>
+    <t xml:space="preserve">Prevent 4 this turn and 4 next turn.</t>
   </si>
   <si>
     <t>cardimages/faceup_synergy.png</t>
@@ -651,6 +651,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="29.28125"/>
+    <col bestFit="1" min="2" max="2" width="17.28125"/>
     <col customWidth="1" min="3" max="3" width="108.421875"/>
   </cols>
   <sheetData>

--- a/acolyte_cards.xlsx
+++ b/acolyte_cards.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Holy Light</t>
   </si>
   <si>
-    <t xml:space="preserve">Heal 2. If healing another player: gain 1 resource</t>
+    <t xml:space="preserve">Heal 2. If healing another player: gain 1 resource.</t>
   </si>
   <si>
     <t xml:space="preserve">cardimages/restore.png</t>
@@ -194,8 +194,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -391,129 +395,129 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="108.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
